--- a/artfynd/A 49255-2021 artfynd.xlsx
+++ b/artfynd/A 49255-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125066160</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>97147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49255-2021 artfynd.xlsx
+++ b/artfynd/A 49255-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125066160</v>
       </c>
       <c r="B2" t="n">
-        <v>97202</v>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,6 +780,113 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125065921</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hagstugan NNV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>597388</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6535560</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Blacksta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49255-2021 artfynd.xlsx
+++ b/artfynd/A 49255-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125066160</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,8 +896,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125065921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>